--- a/calistenia/Progresion_calistenia.xlsx
+++ b/calistenia/Progresion_calistenia.xlsx
@@ -22,19 +22,19 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
-    <t xml:space="preserve">Progresión Calistenia — Foco de mejora: Negativa controlada de dominada</t>
+    <t xml:space="preserve">Progresión Calistenia — Foco de mejora: Dead hang (agarre)</t>
   </si>
   <si>
     <t xml:space="preserve">Celdas amarillas = entrada manual. Sesiones lunes y viernes (casa). Cada fila avanza una sesión. El resto son fórmulas, no sobrescribir. Los demás ejercicios (empuje, piernas, core, día de gimnasio) no llevan esta progresión formal — ver config.json y rutina.md.</t>
   </si>
   <si>
-    <t xml:space="preserve">FASE ACTIVA — Negativa controlada de dominada (bajada lenta desde arriba de la barra)</t>
+    <t xml:space="preserve">FASE ACTIVA — Dead hang: colgado con brazos extendidos, escápulas activas. Foco: agarre.</t>
   </si>
   <si>
     <t xml:space="preserve">Nombre:</t>
   </si>
   <si>
-    <t xml:space="preserve">Negativa controlada de dominada</t>
+    <t xml:space="preserve">Dead hang (barra de techo)</t>
   </si>
   <si>
     <t xml:space="preserve">Objetivo inicial (s):</t>
@@ -46,7 +46,7 @@
     <t xml:space="preserve">Criterio para pasar de fase:</t>
   </si>
   <si>
-    <t xml:space="preserve">Negativa de 8 s controlada x 4 repeticiones limpias, dos sesiones seguidas — entonces se abre la siguiente fase (dominada asistida / parcial) en un nuevo bloque.</t>
+    <t xml:space="preserve">2 series de 40 s limpias, dos sesiones seguidas — entonces se decide con el usuario la siguiente fase (hang a una mano asistido, o reintroducir la negativa en casa) en un nuevo bloque.</t>
   </si>
   <si>
     <t xml:space="preserve">Sesión</t>
@@ -58,22 +58,22 @@
     <t xml:space="preserve">Objetivo (s)</t>
   </si>
   <si>
-    <t xml:space="preserve">Repeticiones</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tiempo bajo tensión (s)</t>
+    <t xml:space="preserve">Series logradas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tiempo total (s)</t>
   </si>
   <si>
     <t xml:space="preserve">Marca estimada (s)</t>
   </si>
   <si>
-    <t xml:space="preserve">Notas (dead hang, sensaciones...)</t>
+    <t xml:space="preserve">Notas (mano izq/dcha, hombro, sensaciones)</t>
   </si>
   <si>
     <t xml:space="preserve">Acumulado</t>
   </si>
   <si>
-    <t xml:space="preserve">Récord tiempo bajo tensión (s)</t>
+    <t xml:space="preserve">Récord tiempo total (s)</t>
   </si>
   <si>
     <t xml:space="preserve">Récord marca estimada (s)</t>
@@ -534,7 +534,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="5" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -542,7 +542,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="5" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -586,11 +586,11 @@
         <v>1</v>
       </c>
       <c r="B11" s="9" t="n">
-        <v>46255</v>
+        <v>46262</v>
       </c>
       <c r="C11" s="8" t="n">
         <f aca="false">IF($B$6="","",$B$6)</f>
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="D11" s="5"/>
       <c r="E11" s="8" t="str">
@@ -609,11 +609,11 @@
       </c>
       <c r="B12" s="10" t="n">
         <f aca="false">IF(B11="","",B11+IF(WEEKDAY(B11,2)=1,4,3))</f>
-        <v>46258</v>
+        <v>46265</v>
       </c>
       <c r="C12" s="8" t="n">
         <f aca="false">IF(C11="","",C11+IF($B$7="",0,$B$7))</f>
-        <v>4.5</v>
+        <v>16</v>
       </c>
       <c r="D12" s="5"/>
       <c r="E12" s="8" t="str">
@@ -632,11 +632,11 @@
       </c>
       <c r="B13" s="10" t="n">
         <f aca="false">IF(B12="","",B12+IF(WEEKDAY(B12,2)=1,4,3))</f>
-        <v>46262</v>
+        <v>46269</v>
       </c>
       <c r="C13" s="8" t="n">
         <f aca="false">IF(C12="","",C12+IF($B$7="",0,$B$7))</f>
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="D13" s="5"/>
       <c r="E13" s="8" t="str">
@@ -655,11 +655,11 @@
       </c>
       <c r="B14" s="10" t="n">
         <f aca="false">IF(B13="","",B13+IF(WEEKDAY(B13,2)=1,4,3))</f>
-        <v>46265</v>
+        <v>46272</v>
       </c>
       <c r="C14" s="8" t="n">
         <f aca="false">IF(C13="","",C13+IF($B$7="",0,$B$7))</f>
-        <v>5.5</v>
+        <v>18</v>
       </c>
       <c r="D14" s="5"/>
       <c r="E14" s="8" t="str">
@@ -678,11 +678,11 @@
       </c>
       <c r="B15" s="10" t="n">
         <f aca="false">IF(B14="","",B14+IF(WEEKDAY(B14,2)=1,4,3))</f>
-        <v>46269</v>
+        <v>46276</v>
       </c>
       <c r="C15" s="8" t="n">
         <f aca="false">IF(C14="","",C14+IF($B$7="",0,$B$7))</f>
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="D15" s="5"/>
       <c r="E15" s="8" t="str">
@@ -701,11 +701,11 @@
       </c>
       <c r="B16" s="10" t="n">
         <f aca="false">IF(B15="","",B15+IF(WEEKDAY(B15,2)=1,4,3))</f>
-        <v>46272</v>
+        <v>46279</v>
       </c>
       <c r="C16" s="8" t="n">
         <f aca="false">IF(C15="","",C15+IF($B$7="",0,$B$7))</f>
-        <v>6.5</v>
+        <v>20</v>
       </c>
       <c r="D16" s="5"/>
       <c r="E16" s="8" t="str">
@@ -724,11 +724,11 @@
       </c>
       <c r="B17" s="10" t="n">
         <f aca="false">IF(B16="","",B16+IF(WEEKDAY(B16,2)=1,4,3))</f>
-        <v>46276</v>
+        <v>46283</v>
       </c>
       <c r="C17" s="8" t="n">
         <f aca="false">IF(C16="","",C16+IF($B$7="",0,$B$7))</f>
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="D17" s="5"/>
       <c r="E17" s="8" t="str">
@@ -747,11 +747,11 @@
       </c>
       <c r="B18" s="10" t="n">
         <f aca="false">IF(B17="","",B17+IF(WEEKDAY(B17,2)=1,4,3))</f>
-        <v>46279</v>
+        <v>46286</v>
       </c>
       <c r="C18" s="8" t="n">
         <f aca="false">IF(C17="","",C17+IF($B$7="",0,$B$7))</f>
-        <v>7.5</v>
+        <v>22</v>
       </c>
       <c r="D18" s="5"/>
       <c r="E18" s="8" t="str">
@@ -770,11 +770,11 @@
       </c>
       <c r="B19" s="10" t="n">
         <f aca="false">IF(B18="","",B18+IF(WEEKDAY(B18,2)=1,4,3))</f>
-        <v>46283</v>
+        <v>46290</v>
       </c>
       <c r="C19" s="8" t="n">
         <f aca="false">IF(C18="","",C18+IF($B$7="",0,$B$7))</f>
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="D19" s="5"/>
       <c r="E19" s="8" t="str">
@@ -793,11 +793,11 @@
       </c>
       <c r="B20" s="10" t="n">
         <f aca="false">IF(B19="","",B19+IF(WEEKDAY(B19,2)=1,4,3))</f>
-        <v>46286</v>
+        <v>46293</v>
       </c>
       <c r="C20" s="8" t="n">
         <f aca="false">IF(C19="","",C19+IF($B$7="",0,$B$7))</f>
-        <v>8.5</v>
+        <v>24</v>
       </c>
       <c r="D20" s="5"/>
       <c r="E20" s="8" t="str">
@@ -816,11 +816,11 @@
       </c>
       <c r="B21" s="10" t="n">
         <f aca="false">IF(B20="","",B20+IF(WEEKDAY(B20,2)=1,4,3))</f>
-        <v>46290</v>
+        <v>46297</v>
       </c>
       <c r="C21" s="8" t="n">
         <f aca="false">IF(C20="","",C20+IF($B$7="",0,$B$7))</f>
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="8" t="str">
@@ -839,11 +839,11 @@
       </c>
       <c r="B22" s="10" t="n">
         <f aca="false">IF(B21="","",B21+IF(WEEKDAY(B21,2)=1,4,3))</f>
-        <v>46293</v>
+        <v>46300</v>
       </c>
       <c r="C22" s="8" t="n">
         <f aca="false">IF(C21="","",C21+IF($B$7="",0,$B$7))</f>
-        <v>9.5</v>
+        <v>26</v>
       </c>
       <c r="D22" s="5"/>
       <c r="E22" s="8" t="str">
@@ -862,11 +862,11 @@
       </c>
       <c r="B23" s="10" t="n">
         <f aca="false">IF(B22="","",B22+IF(WEEKDAY(B22,2)=1,4,3))</f>
-        <v>46297</v>
+        <v>46304</v>
       </c>
       <c r="C23" s="8" t="n">
         <f aca="false">IF(C22="","",C22+IF($B$7="",0,$B$7))</f>
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="D23" s="5"/>
       <c r="E23" s="8" t="str">
@@ -885,11 +885,11 @@
       </c>
       <c r="B24" s="10" t="n">
         <f aca="false">IF(B23="","",B23+IF(WEEKDAY(B23,2)=1,4,3))</f>
-        <v>46300</v>
+        <v>46307</v>
       </c>
       <c r="C24" s="8" t="n">
         <f aca="false">IF(C23="","",C23+IF($B$7="",0,$B$7))</f>
-        <v>10.5</v>
+        <v>28</v>
       </c>
       <c r="D24" s="5"/>
       <c r="E24" s="8" t="str">
@@ -908,11 +908,11 @@
       </c>
       <c r="B25" s="10" t="n">
         <f aca="false">IF(B24="","",B24+IF(WEEKDAY(B24,2)=1,4,3))</f>
-        <v>46304</v>
+        <v>46311</v>
       </c>
       <c r="C25" s="8" t="n">
         <f aca="false">IF(C24="","",C24+IF($B$7="",0,$B$7))</f>
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="D25" s="5"/>
       <c r="E25" s="8" t="str">
@@ -931,11 +931,11 @@
       </c>
       <c r="B26" s="10" t="n">
         <f aca="false">IF(B25="","",B25+IF(WEEKDAY(B25,2)=1,4,3))</f>
-        <v>46307</v>
+        <v>46314</v>
       </c>
       <c r="C26" s="8" t="n">
         <f aca="false">IF(C25="","",C25+IF($B$7="",0,$B$7))</f>
-        <v>11.5</v>
+        <v>30</v>
       </c>
       <c r="D26" s="5"/>
       <c r="E26" s="8" t="str">
@@ -954,11 +954,11 @@
       </c>
       <c r="B27" s="10" t="n">
         <f aca="false">IF(B26="","",B26+IF(WEEKDAY(B26,2)=1,4,3))</f>
-        <v>46311</v>
+        <v>46318</v>
       </c>
       <c r="C27" s="8" t="n">
         <f aca="false">IF(C26="","",C26+IF($B$7="",0,$B$7))</f>
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="D27" s="5"/>
       <c r="E27" s="8" t="str">
@@ -977,11 +977,11 @@
       </c>
       <c r="B28" s="10" t="n">
         <f aca="false">IF(B27="","",B27+IF(WEEKDAY(B27,2)=1,4,3))</f>
-        <v>46314</v>
+        <v>46321</v>
       </c>
       <c r="C28" s="8" t="n">
         <f aca="false">IF(C27="","",C27+IF($B$7="",0,$B$7))</f>
-        <v>12.5</v>
+        <v>32</v>
       </c>
       <c r="D28" s="5"/>
       <c r="E28" s="8" t="str">
@@ -1000,11 +1000,11 @@
       </c>
       <c r="B29" s="10" t="n">
         <f aca="false">IF(B28="","",B28+IF(WEEKDAY(B28,2)=1,4,3))</f>
-        <v>46318</v>
+        <v>46325</v>
       </c>
       <c r="C29" s="8" t="n">
         <f aca="false">IF(C28="","",C28+IF($B$7="",0,$B$7))</f>
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="D29" s="5"/>
       <c r="E29" s="8" t="str">
@@ -1023,11 +1023,11 @@
       </c>
       <c r="B30" s="10" t="n">
         <f aca="false">IF(B29="","",B29+IF(WEEKDAY(B29,2)=1,4,3))</f>
-        <v>46321</v>
+        <v>46328</v>
       </c>
       <c r="C30" s="8" t="n">
         <f aca="false">IF(C29="","",C29+IF($B$7="",0,$B$7))</f>
-        <v>13.5</v>
+        <v>34</v>
       </c>
       <c r="D30" s="5"/>
       <c r="E30" s="8" t="str">
@@ -1046,11 +1046,11 @@
       </c>
       <c r="B31" s="10" t="n">
         <f aca="false">IF(B30="","",B30+IF(WEEKDAY(B30,2)=1,4,3))</f>
-        <v>46325</v>
+        <v>46332</v>
       </c>
       <c r="C31" s="8" t="n">
         <f aca="false">IF(C30="","",C30+IF($B$7="",0,$B$7))</f>
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="D31" s="5"/>
       <c r="E31" s="8" t="str">
@@ -1069,11 +1069,11 @@
       </c>
       <c r="B32" s="10" t="n">
         <f aca="false">IF(B31="","",B31+IF(WEEKDAY(B31,2)=1,4,3))</f>
-        <v>46328</v>
+        <v>46335</v>
       </c>
       <c r="C32" s="8" t="n">
         <f aca="false">IF(C31="","",C31+IF($B$7="",0,$B$7))</f>
-        <v>14.5</v>
+        <v>36</v>
       </c>
       <c r="D32" s="5"/>
       <c r="E32" s="8" t="str">
@@ -1092,11 +1092,11 @@
       </c>
       <c r="B33" s="10" t="n">
         <f aca="false">IF(B32="","",B32+IF(WEEKDAY(B32,2)=1,4,3))</f>
-        <v>46332</v>
+        <v>46339</v>
       </c>
       <c r="C33" s="8" t="n">
         <f aca="false">IF(C32="","",C32+IF($B$7="",0,$B$7))</f>
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="D33" s="5"/>
       <c r="E33" s="8" t="str">
@@ -1115,11 +1115,11 @@
       </c>
       <c r="B34" s="10" t="n">
         <f aca="false">IF(B33="","",B33+IF(WEEKDAY(B33,2)=1,4,3))</f>
-        <v>46335</v>
+        <v>46342</v>
       </c>
       <c r="C34" s="8" t="n">
         <f aca="false">IF(C33="","",C33+IF($B$7="",0,$B$7))</f>
-        <v>15.5</v>
+        <v>38</v>
       </c>
       <c r="D34" s="5"/>
       <c r="E34" s="8" t="str">

--- a/calistenia/Progresion_calistenia.xlsx
+++ b/calistenia/Progresion_calistenia.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
   <si>
     <t xml:space="preserve">Progresión Calistenia — Foco de mejora: Dead hang (agarre)</t>
   </si>
@@ -68,6 +68,12 @@
   </si>
   <si>
     <t xml:space="preserve">Notas (mano izq/dcha, hombro, sensaciones)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 series: 30 / 17 / 10 s. Dos alcanzan el objetivo de 15 s. Mejor marca 30 s (récord). Sin dolor de hombro. Muy cansado: 4ª sesión con un solo día de descanso.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 series: 30 / 15 / 10 s. Objetivo 16 s: solo la 1ª lo pasa. Primera serie clavada en 30 s por 2ª vez (techo). Las series 2 y 3 caen: falta descanso entre series.</t>
   </si>
   <si>
     <t xml:space="preserve">Acumulado</t>
@@ -186,12 +192,16 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -199,15 +209,15 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -215,19 +225,19 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -486,681 +496,689 @@
   <dimension ref="A1:G37"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="34"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+      <c r="G4" s="4"/>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="6" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="5" t="n">
+      <c r="B6" s="6" t="n">
         <v>15</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="5" t="n">
+      <c r="B7" s="6" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="6"/>
-      <c r="D8" s="6"/>
-      <c r="E8" s="6"/>
-      <c r="F8" s="6"/>
-      <c r="G8" s="6"/>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="7" t="s">
+      <c r="C8" s="7"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="7"/>
+      <c r="G8" s="7"/>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C10" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="D10" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="E10" s="7" t="s">
+      <c r="E10" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="F10" s="7" t="s">
+      <c r="F10" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="G10" s="7" t="s">
+      <c r="G10" s="8" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="8" t="n">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="B11" s="9" t="n">
+      <c r="B11" s="10" t="n">
         <v>46262</v>
       </c>
-      <c r="C11" s="8" t="n">
+      <c r="C11" s="9" t="n">
         <f aca="false">IF($B$6="","",$B$6)</f>
         <v>15</v>
       </c>
-      <c r="D11" s="5"/>
-      <c r="E11" s="8" t="str">
+      <c r="D11" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E11" s="9" t="n">
         <f aca="false">IF(OR(C11="",D11=""),"",C11*D11)</f>
-        <v/>
-      </c>
-      <c r="F11" s="8" t="str">
+        <v>30</v>
+      </c>
+      <c r="F11" s="9" t="n">
         <f aca="false">IF(OR(C11="",D11=""),"",C11*(1+0.03*D11))</f>
-        <v/>
-      </c>
-      <c r="G11" s="5"/>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="8" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="G11" s="6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="B12" s="10" t="n">
+      <c r="B12" s="11" t="n">
         <f aca="false">IF(B11="","",B11+IF(WEEKDAY(B11,2)=1,4,3))</f>
         <v>46265</v>
       </c>
-      <c r="C12" s="8" t="n">
+      <c r="C12" s="9" t="n">
         <f aca="false">IF(C11="","",C11+IF($B$7="",0,$B$7))</f>
         <v>16</v>
       </c>
-      <c r="D12" s="5"/>
-      <c r="E12" s="8" t="str">
+      <c r="D12" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" s="9" t="n">
         <f aca="false">IF(OR(C12="",D12=""),"",C12*D12)</f>
-        <v/>
-      </c>
-      <c r="F12" s="8" t="str">
+        <v>16</v>
+      </c>
+      <c r="F12" s="9" t="n">
         <f aca="false">IF(OR(C12="",D12=""),"",C12*(1+0.03*D12))</f>
-        <v/>
-      </c>
-      <c r="G12" s="5"/>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="8" t="n">
+        <v>16.48</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="B13" s="10" t="n">
+      <c r="B13" s="11" t="n">
         <f aca="false">IF(B12="","",B12+IF(WEEKDAY(B12,2)=1,4,3))</f>
         <v>46269</v>
       </c>
-      <c r="C13" s="8" t="n">
+      <c r="C13" s="9" t="n">
         <f aca="false">IF(C12="","",C12+IF($B$7="",0,$B$7))</f>
         <v>17</v>
       </c>
-      <c r="D13" s="5"/>
-      <c r="E13" s="8" t="str">
+      <c r="D13" s="6"/>
+      <c r="E13" s="9" t="str">
         <f aca="false">IF(OR(C13="",D13=""),"",C13*D13)</f>
         <v/>
       </c>
-      <c r="F13" s="8" t="str">
+      <c r="F13" s="9" t="str">
         <f aca="false">IF(OR(C13="",D13=""),"",C13*(1+0.03*D13))</f>
         <v/>
       </c>
-      <c r="G13" s="5"/>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="8" t="n">
+      <c r="G13" s="6"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="B14" s="10" t="n">
+      <c r="B14" s="11" t="n">
         <f aca="false">IF(B13="","",B13+IF(WEEKDAY(B13,2)=1,4,3))</f>
         <v>46272</v>
       </c>
-      <c r="C14" s="8" t="n">
+      <c r="C14" s="9" t="n">
         <f aca="false">IF(C13="","",C13+IF($B$7="",0,$B$7))</f>
         <v>18</v>
       </c>
-      <c r="D14" s="5"/>
-      <c r="E14" s="8" t="str">
+      <c r="D14" s="6"/>
+      <c r="E14" s="9" t="str">
         <f aca="false">IF(OR(C14="",D14=""),"",C14*D14)</f>
         <v/>
       </c>
-      <c r="F14" s="8" t="str">
+      <c r="F14" s="9" t="str">
         <f aca="false">IF(OR(C14="",D14=""),"",C14*(1+0.03*D14))</f>
         <v/>
       </c>
-      <c r="G14" s="5"/>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="8" t="n">
+      <c r="G14" s="6"/>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="B15" s="10" t="n">
+      <c r="B15" s="11" t="n">
         <f aca="false">IF(B14="","",B14+IF(WEEKDAY(B14,2)=1,4,3))</f>
         <v>46276</v>
       </c>
-      <c r="C15" s="8" t="n">
+      <c r="C15" s="9" t="n">
         <f aca="false">IF(C14="","",C14+IF($B$7="",0,$B$7))</f>
         <v>19</v>
       </c>
-      <c r="D15" s="5"/>
-      <c r="E15" s="8" t="str">
+      <c r="D15" s="6"/>
+      <c r="E15" s="9" t="str">
         <f aca="false">IF(OR(C15="",D15=""),"",C15*D15)</f>
         <v/>
       </c>
-      <c r="F15" s="8" t="str">
+      <c r="F15" s="9" t="str">
         <f aca="false">IF(OR(C15="",D15=""),"",C15*(1+0.03*D15))</f>
         <v/>
       </c>
-      <c r="G15" s="5"/>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="8" t="n">
+      <c r="G15" s="6"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="B16" s="10" t="n">
+      <c r="B16" s="11" t="n">
         <f aca="false">IF(B15="","",B15+IF(WEEKDAY(B15,2)=1,4,3))</f>
         <v>46279</v>
       </c>
-      <c r="C16" s="8" t="n">
+      <c r="C16" s="9" t="n">
         <f aca="false">IF(C15="","",C15+IF($B$7="",0,$B$7))</f>
         <v>20</v>
       </c>
-      <c r="D16" s="5"/>
-      <c r="E16" s="8" t="str">
+      <c r="D16" s="6"/>
+      <c r="E16" s="9" t="str">
         <f aca="false">IF(OR(C16="",D16=""),"",C16*D16)</f>
         <v/>
       </c>
-      <c r="F16" s="8" t="str">
+      <c r="F16" s="9" t="str">
         <f aca="false">IF(OR(C16="",D16=""),"",C16*(1+0.03*D16))</f>
         <v/>
       </c>
-      <c r="G16" s="5"/>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="8" t="n">
+      <c r="G16" s="6"/>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="B17" s="10" t="n">
+      <c r="B17" s="11" t="n">
         <f aca="false">IF(B16="","",B16+IF(WEEKDAY(B16,2)=1,4,3))</f>
         <v>46283</v>
       </c>
-      <c r="C17" s="8" t="n">
+      <c r="C17" s="9" t="n">
         <f aca="false">IF(C16="","",C16+IF($B$7="",0,$B$7))</f>
         <v>21</v>
       </c>
-      <c r="D17" s="5"/>
-      <c r="E17" s="8" t="str">
+      <c r="D17" s="6"/>
+      <c r="E17" s="9" t="str">
         <f aca="false">IF(OR(C17="",D17=""),"",C17*D17)</f>
         <v/>
       </c>
-      <c r="F17" s="8" t="str">
+      <c r="F17" s="9" t="str">
         <f aca="false">IF(OR(C17="",D17=""),"",C17*(1+0.03*D17))</f>
         <v/>
       </c>
-      <c r="G17" s="5"/>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="8" t="n">
+      <c r="G17" s="6"/>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="B18" s="10" t="n">
+      <c r="B18" s="11" t="n">
         <f aca="false">IF(B17="","",B17+IF(WEEKDAY(B17,2)=1,4,3))</f>
         <v>46286</v>
       </c>
-      <c r="C18" s="8" t="n">
+      <c r="C18" s="9" t="n">
         <f aca="false">IF(C17="","",C17+IF($B$7="",0,$B$7))</f>
         <v>22</v>
       </c>
-      <c r="D18" s="5"/>
-      <c r="E18" s="8" t="str">
+      <c r="D18" s="6"/>
+      <c r="E18" s="9" t="str">
         <f aca="false">IF(OR(C18="",D18=""),"",C18*D18)</f>
         <v/>
       </c>
-      <c r="F18" s="8" t="str">
+      <c r="F18" s="9" t="str">
         <f aca="false">IF(OR(C18="",D18=""),"",C18*(1+0.03*D18))</f>
         <v/>
       </c>
-      <c r="G18" s="5"/>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="8" t="n">
+      <c r="G18" s="6"/>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="9" t="n">
         <v>9</v>
       </c>
-      <c r="B19" s="10" t="n">
+      <c r="B19" s="11" t="n">
         <f aca="false">IF(B18="","",B18+IF(WEEKDAY(B18,2)=1,4,3))</f>
         <v>46290</v>
       </c>
-      <c r="C19" s="8" t="n">
+      <c r="C19" s="9" t="n">
         <f aca="false">IF(C18="","",C18+IF($B$7="",0,$B$7))</f>
         <v>23</v>
       </c>
-      <c r="D19" s="5"/>
-      <c r="E19" s="8" t="str">
+      <c r="D19" s="6"/>
+      <c r="E19" s="9" t="str">
         <f aca="false">IF(OR(C19="",D19=""),"",C19*D19)</f>
         <v/>
       </c>
-      <c r="F19" s="8" t="str">
+      <c r="F19" s="9" t="str">
         <f aca="false">IF(OR(C19="",D19=""),"",C19*(1+0.03*D19))</f>
         <v/>
       </c>
-      <c r="G19" s="5"/>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="8" t="n">
+      <c r="G19" s="6"/>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="B20" s="10" t="n">
+      <c r="B20" s="11" t="n">
         <f aca="false">IF(B19="","",B19+IF(WEEKDAY(B19,2)=1,4,3))</f>
         <v>46293</v>
       </c>
-      <c r="C20" s="8" t="n">
+      <c r="C20" s="9" t="n">
         <f aca="false">IF(C19="","",C19+IF($B$7="",0,$B$7))</f>
         <v>24</v>
       </c>
-      <c r="D20" s="5"/>
-      <c r="E20" s="8" t="str">
+      <c r="D20" s="6"/>
+      <c r="E20" s="9" t="str">
         <f aca="false">IF(OR(C20="",D20=""),"",C20*D20)</f>
         <v/>
       </c>
-      <c r="F20" s="8" t="str">
+      <c r="F20" s="9" t="str">
         <f aca="false">IF(OR(C20="",D20=""),"",C20*(1+0.03*D20))</f>
         <v/>
       </c>
-      <c r="G20" s="5"/>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="8" t="n">
+      <c r="G20" s="6"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="9" t="n">
         <v>11</v>
       </c>
-      <c r="B21" s="10" t="n">
+      <c r="B21" s="11" t="n">
         <f aca="false">IF(B20="","",B20+IF(WEEKDAY(B20,2)=1,4,3))</f>
         <v>46297</v>
       </c>
-      <c r="C21" s="8" t="n">
+      <c r="C21" s="9" t="n">
         <f aca="false">IF(C20="","",C20+IF($B$7="",0,$B$7))</f>
         <v>25</v>
       </c>
-      <c r="D21" s="5"/>
-      <c r="E21" s="8" t="str">
+      <c r="D21" s="6"/>
+      <c r="E21" s="9" t="str">
         <f aca="false">IF(OR(C21="",D21=""),"",C21*D21)</f>
         <v/>
       </c>
-      <c r="F21" s="8" t="str">
+      <c r="F21" s="9" t="str">
         <f aca="false">IF(OR(C21="",D21=""),"",C21*(1+0.03*D21))</f>
         <v/>
       </c>
-      <c r="G21" s="5"/>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="8" t="n">
+      <c r="G21" s="6"/>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="B22" s="10" t="n">
+      <c r="B22" s="11" t="n">
         <f aca="false">IF(B21="","",B21+IF(WEEKDAY(B21,2)=1,4,3))</f>
         <v>46300</v>
       </c>
-      <c r="C22" s="8" t="n">
+      <c r="C22" s="9" t="n">
         <f aca="false">IF(C21="","",C21+IF($B$7="",0,$B$7))</f>
         <v>26</v>
       </c>
-      <c r="D22" s="5"/>
-      <c r="E22" s="8" t="str">
+      <c r="D22" s="6"/>
+      <c r="E22" s="9" t="str">
         <f aca="false">IF(OR(C22="",D22=""),"",C22*D22)</f>
         <v/>
       </c>
-      <c r="F22" s="8" t="str">
+      <c r="F22" s="9" t="str">
         <f aca="false">IF(OR(C22="",D22=""),"",C22*(1+0.03*D22))</f>
         <v/>
       </c>
-      <c r="G22" s="5"/>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="8" t="n">
+      <c r="G22" s="6"/>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="9" t="n">
         <v>13</v>
       </c>
-      <c r="B23" s="10" t="n">
+      <c r="B23" s="11" t="n">
         <f aca="false">IF(B22="","",B22+IF(WEEKDAY(B22,2)=1,4,3))</f>
         <v>46304</v>
       </c>
-      <c r="C23" s="8" t="n">
+      <c r="C23" s="9" t="n">
         <f aca="false">IF(C22="","",C22+IF($B$7="",0,$B$7))</f>
         <v>27</v>
       </c>
-      <c r="D23" s="5"/>
-      <c r="E23" s="8" t="str">
+      <c r="D23" s="6"/>
+      <c r="E23" s="9" t="str">
         <f aca="false">IF(OR(C23="",D23=""),"",C23*D23)</f>
         <v/>
       </c>
-      <c r="F23" s="8" t="str">
+      <c r="F23" s="9" t="str">
         <f aca="false">IF(OR(C23="",D23=""),"",C23*(1+0.03*D23))</f>
         <v/>
       </c>
-      <c r="G23" s="5"/>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="8" t="n">
+      <c r="G23" s="6"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="9" t="n">
         <v>14</v>
       </c>
-      <c r="B24" s="10" t="n">
+      <c r="B24" s="11" t="n">
         <f aca="false">IF(B23="","",B23+IF(WEEKDAY(B23,2)=1,4,3))</f>
         <v>46307</v>
       </c>
-      <c r="C24" s="8" t="n">
+      <c r="C24" s="9" t="n">
         <f aca="false">IF(C23="","",C23+IF($B$7="",0,$B$7))</f>
         <v>28</v>
       </c>
-      <c r="D24" s="5"/>
-      <c r="E24" s="8" t="str">
+      <c r="D24" s="6"/>
+      <c r="E24" s="9" t="str">
         <f aca="false">IF(OR(C24="",D24=""),"",C24*D24)</f>
         <v/>
       </c>
-      <c r="F24" s="8" t="str">
+      <c r="F24" s="9" t="str">
         <f aca="false">IF(OR(C24="",D24=""),"",C24*(1+0.03*D24))</f>
         <v/>
       </c>
-      <c r="G24" s="5"/>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="8" t="n">
+      <c r="G24" s="6"/>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="B25" s="10" t="n">
+      <c r="B25" s="11" t="n">
         <f aca="false">IF(B24="","",B24+IF(WEEKDAY(B24,2)=1,4,3))</f>
         <v>46311</v>
       </c>
-      <c r="C25" s="8" t="n">
+      <c r="C25" s="9" t="n">
         <f aca="false">IF(C24="","",C24+IF($B$7="",0,$B$7))</f>
         <v>29</v>
       </c>
-      <c r="D25" s="5"/>
-      <c r="E25" s="8" t="str">
+      <c r="D25" s="6"/>
+      <c r="E25" s="9" t="str">
         <f aca="false">IF(OR(C25="",D25=""),"",C25*D25)</f>
         <v/>
       </c>
-      <c r="F25" s="8" t="str">
+      <c r="F25" s="9" t="str">
         <f aca="false">IF(OR(C25="",D25=""),"",C25*(1+0.03*D25))</f>
         <v/>
       </c>
-      <c r="G25" s="5"/>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="8" t="n">
+      <c r="G25" s="6"/>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="9" t="n">
         <v>16</v>
       </c>
-      <c r="B26" s="10" t="n">
+      <c r="B26" s="11" t="n">
         <f aca="false">IF(B25="","",B25+IF(WEEKDAY(B25,2)=1,4,3))</f>
         <v>46314</v>
       </c>
-      <c r="C26" s="8" t="n">
+      <c r="C26" s="9" t="n">
         <f aca="false">IF(C25="","",C25+IF($B$7="",0,$B$7))</f>
         <v>30</v>
       </c>
-      <c r="D26" s="5"/>
-      <c r="E26" s="8" t="str">
+      <c r="D26" s="6"/>
+      <c r="E26" s="9" t="str">
         <f aca="false">IF(OR(C26="",D26=""),"",C26*D26)</f>
         <v/>
       </c>
-      <c r="F26" s="8" t="str">
+      <c r="F26" s="9" t="str">
         <f aca="false">IF(OR(C26="",D26=""),"",C26*(1+0.03*D26))</f>
         <v/>
       </c>
-      <c r="G26" s="5"/>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="8" t="n">
+      <c r="G26" s="6"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="9" t="n">
         <v>17</v>
       </c>
-      <c r="B27" s="10" t="n">
+      <c r="B27" s="11" t="n">
         <f aca="false">IF(B26="","",B26+IF(WEEKDAY(B26,2)=1,4,3))</f>
         <v>46318</v>
       </c>
-      <c r="C27" s="8" t="n">
+      <c r="C27" s="9" t="n">
         <f aca="false">IF(C26="","",C26+IF($B$7="",0,$B$7))</f>
         <v>31</v>
       </c>
-      <c r="D27" s="5"/>
-      <c r="E27" s="8" t="str">
+      <c r="D27" s="6"/>
+      <c r="E27" s="9" t="str">
         <f aca="false">IF(OR(C27="",D27=""),"",C27*D27)</f>
         <v/>
       </c>
-      <c r="F27" s="8" t="str">
+      <c r="F27" s="9" t="str">
         <f aca="false">IF(OR(C27="",D27=""),"",C27*(1+0.03*D27))</f>
         <v/>
       </c>
-      <c r="G27" s="5"/>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="8" t="n">
+      <c r="G27" s="6"/>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="9" t="n">
         <v>18</v>
       </c>
-      <c r="B28" s="10" t="n">
+      <c r="B28" s="11" t="n">
         <f aca="false">IF(B27="","",B27+IF(WEEKDAY(B27,2)=1,4,3))</f>
         <v>46321</v>
       </c>
-      <c r="C28" s="8" t="n">
+      <c r="C28" s="9" t="n">
         <f aca="false">IF(C27="","",C27+IF($B$7="",0,$B$7))</f>
         <v>32</v>
       </c>
-      <c r="D28" s="5"/>
-      <c r="E28" s="8" t="str">
+      <c r="D28" s="6"/>
+      <c r="E28" s="9" t="str">
         <f aca="false">IF(OR(C28="",D28=""),"",C28*D28)</f>
         <v/>
       </c>
-      <c r="F28" s="8" t="str">
+      <c r="F28" s="9" t="str">
         <f aca="false">IF(OR(C28="",D28=""),"",C28*(1+0.03*D28))</f>
         <v/>
       </c>
-      <c r="G28" s="5"/>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="8" t="n">
+      <c r="G28" s="6"/>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="9" t="n">
         <v>19</v>
       </c>
-      <c r="B29" s="10" t="n">
+      <c r="B29" s="11" t="n">
         <f aca="false">IF(B28="","",B28+IF(WEEKDAY(B28,2)=1,4,3))</f>
         <v>46325</v>
       </c>
-      <c r="C29" s="8" t="n">
+      <c r="C29" s="9" t="n">
         <f aca="false">IF(C28="","",C28+IF($B$7="",0,$B$7))</f>
         <v>33</v>
       </c>
-      <c r="D29" s="5"/>
-      <c r="E29" s="8" t="str">
+      <c r="D29" s="6"/>
+      <c r="E29" s="9" t="str">
         <f aca="false">IF(OR(C29="",D29=""),"",C29*D29)</f>
         <v/>
       </c>
-      <c r="F29" s="8" t="str">
+      <c r="F29" s="9" t="str">
         <f aca="false">IF(OR(C29="",D29=""),"",C29*(1+0.03*D29))</f>
         <v/>
       </c>
-      <c r="G29" s="5"/>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="8" t="n">
+      <c r="G29" s="6"/>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="B30" s="10" t="n">
+      <c r="B30" s="11" t="n">
         <f aca="false">IF(B29="","",B29+IF(WEEKDAY(B29,2)=1,4,3))</f>
         <v>46328</v>
       </c>
-      <c r="C30" s="8" t="n">
+      <c r="C30" s="9" t="n">
         <f aca="false">IF(C29="","",C29+IF($B$7="",0,$B$7))</f>
         <v>34</v>
       </c>
-      <c r="D30" s="5"/>
-      <c r="E30" s="8" t="str">
+      <c r="D30" s="6"/>
+      <c r="E30" s="9" t="str">
         <f aca="false">IF(OR(C30="",D30=""),"",C30*D30)</f>
         <v/>
       </c>
-      <c r="F30" s="8" t="str">
+      <c r="F30" s="9" t="str">
         <f aca="false">IF(OR(C30="",D30=""),"",C30*(1+0.03*D30))</f>
         <v/>
       </c>
-      <c r="G30" s="5"/>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="8" t="n">
+      <c r="G30" s="6"/>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="9" t="n">
         <v>21</v>
       </c>
-      <c r="B31" s="10" t="n">
+      <c r="B31" s="11" t="n">
         <f aca="false">IF(B30="","",B30+IF(WEEKDAY(B30,2)=1,4,3))</f>
         <v>46332</v>
       </c>
-      <c r="C31" s="8" t="n">
+      <c r="C31" s="9" t="n">
         <f aca="false">IF(C30="","",C30+IF($B$7="",0,$B$7))</f>
         <v>35</v>
       </c>
-      <c r="D31" s="5"/>
-      <c r="E31" s="8" t="str">
+      <c r="D31" s="6"/>
+      <c r="E31" s="9" t="str">
         <f aca="false">IF(OR(C31="",D31=""),"",C31*D31)</f>
         <v/>
       </c>
-      <c r="F31" s="8" t="str">
+      <c r="F31" s="9" t="str">
         <f aca="false">IF(OR(C31="",D31=""),"",C31*(1+0.03*D31))</f>
         <v/>
       </c>
-      <c r="G31" s="5"/>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="8" t="n">
+      <c r="G31" s="6"/>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="9" t="n">
         <v>22</v>
       </c>
-      <c r="B32" s="10" t="n">
+      <c r="B32" s="11" t="n">
         <f aca="false">IF(B31="","",B31+IF(WEEKDAY(B31,2)=1,4,3))</f>
         <v>46335</v>
       </c>
-      <c r="C32" s="8" t="n">
+      <c r="C32" s="9" t="n">
         <f aca="false">IF(C31="","",C31+IF($B$7="",0,$B$7))</f>
         <v>36</v>
       </c>
-      <c r="D32" s="5"/>
-      <c r="E32" s="8" t="str">
+      <c r="D32" s="6"/>
+      <c r="E32" s="9" t="str">
         <f aca="false">IF(OR(C32="",D32=""),"",C32*D32)</f>
         <v/>
       </c>
-      <c r="F32" s="8" t="str">
+      <c r="F32" s="9" t="str">
         <f aca="false">IF(OR(C32="",D32=""),"",C32*(1+0.03*D32))</f>
         <v/>
       </c>
-      <c r="G32" s="5"/>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="8" t="n">
+      <c r="G32" s="6"/>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="9" t="n">
         <v>23</v>
       </c>
-      <c r="B33" s="10" t="n">
+      <c r="B33" s="11" t="n">
         <f aca="false">IF(B32="","",B32+IF(WEEKDAY(B32,2)=1,4,3))</f>
         <v>46339</v>
       </c>
-      <c r="C33" s="8" t="n">
+      <c r="C33" s="9" t="n">
         <f aca="false">IF(C32="","",C32+IF($B$7="",0,$B$7))</f>
         <v>37</v>
       </c>
-      <c r="D33" s="5"/>
-      <c r="E33" s="8" t="str">
+      <c r="D33" s="6"/>
+      <c r="E33" s="9" t="str">
         <f aca="false">IF(OR(C33="",D33=""),"",C33*D33)</f>
         <v/>
       </c>
-      <c r="F33" s="8" t="str">
+      <c r="F33" s="9" t="str">
         <f aca="false">IF(OR(C33="",D33=""),"",C33*(1+0.03*D33))</f>
         <v/>
       </c>
-      <c r="G33" s="5"/>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="8" t="n">
+      <c r="G33" s="6"/>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="9" t="n">
         <v>24</v>
       </c>
-      <c r="B34" s="10" t="n">
+      <c r="B34" s="11" t="n">
         <f aca="false">IF(B33="","",B33+IF(WEEKDAY(B33,2)=1,4,3))</f>
         <v>46342</v>
       </c>
-      <c r="C34" s="8" t="n">
+      <c r="C34" s="9" t="n">
         <f aca="false">IF(C33="","",C33+IF($B$7="",0,$B$7))</f>
         <v>38</v>
       </c>
-      <c r="D34" s="5"/>
-      <c r="E34" s="8" t="str">
+      <c r="D34" s="6"/>
+      <c r="E34" s="9" t="str">
         <f aca="false">IF(OR(C34="",D34=""),"",C34*D34)</f>
         <v/>
       </c>
-      <c r="F34" s="8" t="str">
+      <c r="F34" s="9" t="str">
         <f aca="false">IF(OR(C34="",D34=""),"",C34*(1+0.03*D34))</f>
         <v/>
       </c>
-      <c r="G34" s="5"/>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D35" s="8" t="n">
+      <c r="G34" s="6"/>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D35" s="9" t="n">
         <f aca="false">SUM(D11:D34)</f>
-        <v>0</v>
-      </c>
-      <c r="E35" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="E35" s="9" t="n">
         <f aca="false">SUM(E11:E34)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="E36" s="8" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E36" s="9" t="n">
         <f aca="false">MAX(E11:E34)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="F37" s="8" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F37" s="9" t="n">
         <f aca="false">MAX(F11:F34)</f>
-        <v>0</v>
+        <v>16.48</v>
       </c>
     </row>
   </sheetData>

--- a/calistenia/Progresion_calistenia.xlsx
+++ b/calistenia/Progresion_calistenia.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t xml:space="preserve">Progresión Calistenia — Foco de mejora: Dead hang (agarre)</t>
   </si>
@@ -74,6 +74,9 @@
   </si>
   <si>
     <t xml:space="preserve">3 series: 30 / 15 / 10 s. Objetivo 16 s: solo la 1ª lo pasa. Primera serie clavada en 30 s por 2ª vez (techo). Las series 2 y 3 caen: falta descanso entre series.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 series: 20 / 20 / 13 s. Objetivo 17 s: 2 series lo pasan. Perfil mucho más plano que antes (30/15/10 -&gt; 20/20/13): la 2a serie sube 5 s. Una semana sin sesiones registradas entre esta y la anterior.</t>
   </si>
   <si>
     <t xml:space="preserve">Acumulado</t>
@@ -649,23 +652,26 @@
         <v>3</v>
       </c>
       <c r="B13" s="11" t="n">
-        <f aca="false">IF(B12="","",B12+IF(WEEKDAY(B12,2)=1,4,3))</f>
-        <v>46269</v>
+        <v>46272</v>
       </c>
       <c r="C13" s="9" t="n">
         <f aca="false">IF(C12="","",C12+IF($B$7="",0,$B$7))</f>
         <v>17</v>
       </c>
-      <c r="D13" s="6"/>
-      <c r="E13" s="9" t="str">
+      <c r="D13" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E13" s="9" t="n">
         <f aca="false">IF(OR(C13="",D13=""),"",C13*D13)</f>
-        <v/>
-      </c>
-      <c r="F13" s="9" t="str">
+        <v>34</v>
+      </c>
+      <c r="F13" s="9" t="n">
         <f aca="false">IF(OR(C13="",D13=""),"",C13*(1+0.03*D13))</f>
-        <v/>
-      </c>
-      <c r="G13" s="6"/>
+        <v>18.02</v>
+      </c>
+      <c r="G13" s="6" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="9" t="n">
@@ -673,7 +679,7 @@
       </c>
       <c r="B14" s="11" t="n">
         <f aca="false">IF(B13="","",B13+IF(WEEKDAY(B13,2)=1,4,3))</f>
-        <v>46272</v>
+        <v>46276</v>
       </c>
       <c r="C14" s="9" t="n">
         <f aca="false">IF(C13="","",C13+IF($B$7="",0,$B$7))</f>
@@ -696,7 +702,7 @@
       </c>
       <c r="B15" s="11" t="n">
         <f aca="false">IF(B14="","",B14+IF(WEEKDAY(B14,2)=1,4,3))</f>
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C15" s="9" t="n">
         <f aca="false">IF(C14="","",C14+IF($B$7="",0,$B$7))</f>
@@ -719,7 +725,7 @@
       </c>
       <c r="B16" s="11" t="n">
         <f aca="false">IF(B15="","",B15+IF(WEEKDAY(B15,2)=1,4,3))</f>
-        <v>46279</v>
+        <v>46283</v>
       </c>
       <c r="C16" s="9" t="n">
         <f aca="false">IF(C15="","",C15+IF($B$7="",0,$B$7))</f>
@@ -742,7 +748,7 @@
       </c>
       <c r="B17" s="11" t="n">
         <f aca="false">IF(B16="","",B16+IF(WEEKDAY(B16,2)=1,4,3))</f>
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="C17" s="9" t="n">
         <f aca="false">IF(C16="","",C16+IF($B$7="",0,$B$7))</f>
@@ -765,7 +771,7 @@
       </c>
       <c r="B18" s="11" t="n">
         <f aca="false">IF(B17="","",B17+IF(WEEKDAY(B17,2)=1,4,3))</f>
-        <v>46286</v>
+        <v>46290</v>
       </c>
       <c r="C18" s="9" t="n">
         <f aca="false">IF(C17="","",C17+IF($B$7="",0,$B$7))</f>
@@ -788,7 +794,7 @@
       </c>
       <c r="B19" s="11" t="n">
         <f aca="false">IF(B18="","",B18+IF(WEEKDAY(B18,2)=1,4,3))</f>
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="C19" s="9" t="n">
         <f aca="false">IF(C18="","",C18+IF($B$7="",0,$B$7))</f>
@@ -811,7 +817,7 @@
       </c>
       <c r="B20" s="11" t="n">
         <f aca="false">IF(B19="","",B19+IF(WEEKDAY(B19,2)=1,4,3))</f>
-        <v>46293</v>
+        <v>46297</v>
       </c>
       <c r="C20" s="9" t="n">
         <f aca="false">IF(C19="","",C19+IF($B$7="",0,$B$7))</f>
@@ -834,7 +840,7 @@
       </c>
       <c r="B21" s="11" t="n">
         <f aca="false">IF(B20="","",B20+IF(WEEKDAY(B20,2)=1,4,3))</f>
-        <v>46297</v>
+        <v>46300</v>
       </c>
       <c r="C21" s="9" t="n">
         <f aca="false">IF(C20="","",C20+IF($B$7="",0,$B$7))</f>
@@ -857,7 +863,7 @@
       </c>
       <c r="B22" s="11" t="n">
         <f aca="false">IF(B21="","",B21+IF(WEEKDAY(B21,2)=1,4,3))</f>
-        <v>46300</v>
+        <v>46304</v>
       </c>
       <c r="C22" s="9" t="n">
         <f aca="false">IF(C21="","",C21+IF($B$7="",0,$B$7))</f>
@@ -880,7 +886,7 @@
       </c>
       <c r="B23" s="11" t="n">
         <f aca="false">IF(B22="","",B22+IF(WEEKDAY(B22,2)=1,4,3))</f>
-        <v>46304</v>
+        <v>46307</v>
       </c>
       <c r="C23" s="9" t="n">
         <f aca="false">IF(C22="","",C22+IF($B$7="",0,$B$7))</f>
@@ -903,7 +909,7 @@
       </c>
       <c r="B24" s="11" t="n">
         <f aca="false">IF(B23="","",B23+IF(WEEKDAY(B23,2)=1,4,3))</f>
-        <v>46307</v>
+        <v>46311</v>
       </c>
       <c r="C24" s="9" t="n">
         <f aca="false">IF(C23="","",C23+IF($B$7="",0,$B$7))</f>
@@ -926,7 +932,7 @@
       </c>
       <c r="B25" s="11" t="n">
         <f aca="false">IF(B24="","",B24+IF(WEEKDAY(B24,2)=1,4,3))</f>
-        <v>46311</v>
+        <v>46314</v>
       </c>
       <c r="C25" s="9" t="n">
         <f aca="false">IF(C24="","",C24+IF($B$7="",0,$B$7))</f>
@@ -949,7 +955,7 @@
       </c>
       <c r="B26" s="11" t="n">
         <f aca="false">IF(B25="","",B25+IF(WEEKDAY(B25,2)=1,4,3))</f>
-        <v>46314</v>
+        <v>46318</v>
       </c>
       <c r="C26" s="9" t="n">
         <f aca="false">IF(C25="","",C25+IF($B$7="",0,$B$7))</f>
@@ -972,7 +978,7 @@
       </c>
       <c r="B27" s="11" t="n">
         <f aca="false">IF(B26="","",B26+IF(WEEKDAY(B26,2)=1,4,3))</f>
-        <v>46318</v>
+        <v>46321</v>
       </c>
       <c r="C27" s="9" t="n">
         <f aca="false">IF(C26="","",C26+IF($B$7="",0,$B$7))</f>
@@ -995,7 +1001,7 @@
       </c>
       <c r="B28" s="11" t="n">
         <f aca="false">IF(B27="","",B27+IF(WEEKDAY(B27,2)=1,4,3))</f>
-        <v>46321</v>
+        <v>46325</v>
       </c>
       <c r="C28" s="9" t="n">
         <f aca="false">IF(C27="","",C27+IF($B$7="",0,$B$7))</f>
@@ -1018,7 +1024,7 @@
       </c>
       <c r="B29" s="11" t="n">
         <f aca="false">IF(B28="","",B28+IF(WEEKDAY(B28,2)=1,4,3))</f>
-        <v>46325</v>
+        <v>46328</v>
       </c>
       <c r="C29" s="9" t="n">
         <f aca="false">IF(C28="","",C28+IF($B$7="",0,$B$7))</f>
@@ -1041,7 +1047,7 @@
       </c>
       <c r="B30" s="11" t="n">
         <f aca="false">IF(B29="","",B29+IF(WEEKDAY(B29,2)=1,4,3))</f>
-        <v>46328</v>
+        <v>46332</v>
       </c>
       <c r="C30" s="9" t="n">
         <f aca="false">IF(C29="","",C29+IF($B$7="",0,$B$7))</f>
@@ -1064,7 +1070,7 @@
       </c>
       <c r="B31" s="11" t="n">
         <f aca="false">IF(B30="","",B30+IF(WEEKDAY(B30,2)=1,4,3))</f>
-        <v>46332</v>
+        <v>46335</v>
       </c>
       <c r="C31" s="9" t="n">
         <f aca="false">IF(C30="","",C30+IF($B$7="",0,$B$7))</f>
@@ -1087,7 +1093,7 @@
       </c>
       <c r="B32" s="11" t="n">
         <f aca="false">IF(B31="","",B31+IF(WEEKDAY(B31,2)=1,4,3))</f>
-        <v>46335</v>
+        <v>46339</v>
       </c>
       <c r="C32" s="9" t="n">
         <f aca="false">IF(C31="","",C31+IF($B$7="",0,$B$7))</f>
@@ -1110,7 +1116,7 @@
       </c>
       <c r="B33" s="11" t="n">
         <f aca="false">IF(B32="","",B32+IF(WEEKDAY(B32,2)=1,4,3))</f>
-        <v>46339</v>
+        <v>46342</v>
       </c>
       <c r="C33" s="9" t="n">
         <f aca="false">IF(C32="","",C32+IF($B$7="",0,$B$7))</f>
@@ -1133,7 +1139,7 @@
       </c>
       <c r="B34" s="11" t="n">
         <f aca="false">IF(B33="","",B33+IF(WEEKDAY(B33,2)=1,4,3))</f>
-        <v>46342</v>
+        <v>46346</v>
       </c>
       <c r="C34" s="9" t="n">
         <f aca="false">IF(C33="","",C33+IF($B$7="",0,$B$7))</f>
@@ -1152,33 +1158,33 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D35" s="9" t="n">
         <f aca="false">SUM(D11:D34)</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E35" s="9" t="n">
         <f aca="false">SUM(E11:E34)</f>
-        <v>46</v>
+        <v>80</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E36" s="9" t="n">
         <f aca="false">MAX(E11:E34)</f>
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F37" s="9" t="n">
         <f aca="false">MAX(F11:F34)</f>
-        <v>16.48</v>
+        <v>18.02</v>
       </c>
     </row>
   </sheetData>

--- a/calistenia/Progresion_calistenia.xlsx
+++ b/calistenia/Progresion_calistenia.xlsx
@@ -5,10 +5,11 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Ciclo" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="Ciclo 1 (histórico)" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="Ciclo 2" sheetId="2" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -20,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="39">
   <si>
     <t xml:space="preserve">Progresión Calistenia — Foco de mejora: Dead hang (agarre)</t>
   </si>
@@ -79,6 +80,9 @@
     <t xml:space="preserve">3 series: 20 / 20 / 13 s. Objetivo 17 s: 2 series lo pasan. Perfil mucho más plano que antes (30/15/10 -&gt; 20/20/13): la 2a serie sube 5 s. Una semana sin sesiones registradas entre esta y la anterior.</t>
   </si>
   <si>
+    <t xml:space="preserve">3 series: 30 / 17 / 14 s = 61 s totales (mejor total del ciclo). Objetivo 18 s: solo la 1a serie lo pasa. Pico recuperado (30 s) y 3a serie la mejor hasta ahora (14 s).</t>
+  </si>
+  <si>
     <t xml:space="preserve">Acumulado</t>
   </si>
   <si>
@@ -86,6 +90,54 @@
   </si>
   <si>
     <t xml:space="preserve">Récord marca estimada (s)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Progresión Calistenia — Ciclo 2: Dead hang, esquema serie máxima</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Celdas amarillas = entrada manual. Esquema desde 14/09/2026: 1 SERIE MÁXIMA en fresco (es la que cuenta y la que se progresa) + 2 series de respaldo a tiempo fijo cómodo, solo para sumar volumen de agarre. El dead hang va al principio del bloque de tracción.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HISTÓRICO CICLO 1 — mejor serie por sesión: 28/08: 30 s · 31/08: 30 s · 07/09: 20 s · 11/09: 30 s. Totales: 57 · 55 · 53 · 61 s.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dead hang — serie máxima</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Objetivo inicial serie máx. (s):</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Respaldo pautado:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 series x 15 s, sin llegar al límite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regla de no progresión:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Si la serie máxima no alcanza el objetivo dos sesiones seguidas, se congela el objetivo hasta superarlo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SERIE MÁX. (s)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Respaldo (s tot.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total sesión (s)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Notas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Récord serie máxima (s)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mejor total de sesión (s)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acumulado total (s)</t>
   </si>
 </sst>
 </file>
@@ -195,7 +247,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="20">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -241,6 +293,38 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -685,16 +769,20 @@
         <f aca="false">IF(C13="","",C13+IF($B$7="",0,$B$7))</f>
         <v>18</v>
       </c>
-      <c r="D14" s="6"/>
-      <c r="E14" s="9" t="str">
+      <c r="D14" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" s="9" t="n">
         <f aca="false">IF(OR(C14="",D14=""),"",C14*D14)</f>
-        <v/>
-      </c>
-      <c r="F14" s="9" t="str">
+        <v>18</v>
+      </c>
+      <c r="F14" s="9" t="n">
         <f aca="false">IF(OR(C14="",D14=""),"",C14*(1+0.03*D14))</f>
-        <v/>
-      </c>
-      <c r="G14" s="6"/>
+        <v>18.54</v>
+      </c>
+      <c r="G14" s="6" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="9" t="n">
@@ -1158,20 +1246,20 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D35" s="9" t="n">
         <f aca="false">SUM(D11:D34)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E35" s="9" t="n">
         <f aca="false">SUM(E11:E34)</f>
-        <v>80</v>
+        <v>98</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E36" s="9" t="n">
         <f aca="false">MAX(E11:E34)</f>
@@ -1180,11 +1268,11 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F37" s="9" t="n">
         <f aca="false">MAX(F11:F34)</f>
-        <v>18.02</v>
+        <v>18.54</v>
       </c>
     </row>
   </sheetData>
@@ -1201,4 +1289,637 @@
     <oddFooter/>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:G38"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="0" width="17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="38"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="12" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4" s="13"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="13"/>
+      <c r="F4" s="13"/>
+      <c r="G4" s="13"/>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="15" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="B6" s="15" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="15" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" s="15" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C9" s="7"/>
+      <c r="D9" s="7"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="7"/>
+      <c r="G9" s="7"/>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="D11" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="E11" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="F11" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="G11" s="16" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="B12" s="18" t="n">
+        <v>46279</v>
+      </c>
+      <c r="C12" s="17" t="n">
+        <f aca="false">IF($B$6="","",$B$6)</f>
+        <v>31</v>
+      </c>
+      <c r="D12" s="15"/>
+      <c r="E12" s="15"/>
+      <c r="F12" s="17" t="str">
+        <f aca="false">IF(D12="","",D12+IF(E12="",0,E12))</f>
+        <v/>
+      </c>
+      <c r="G12" s="15"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="B13" s="19" t="n">
+        <f aca="false">IF(B12="","",B12+IF(WEEKDAY(B12,2)=1,4,3))</f>
+        <v>46283</v>
+      </c>
+      <c r="C13" s="17" t="n">
+        <f aca="false">IF(C12="","",C12+IF($B$7="",0,$B$7))</f>
+        <v>32</v>
+      </c>
+      <c r="D13" s="15"/>
+      <c r="E13" s="15"/>
+      <c r="F13" s="17" t="str">
+        <f aca="false">IF(D13="","",D13+IF(E13="",0,E13))</f>
+        <v/>
+      </c>
+      <c r="G13" s="15"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="B14" s="19" t="n">
+        <f aca="false">IF(B13="","",B13+IF(WEEKDAY(B13,2)=1,4,3))</f>
+        <v>46286</v>
+      </c>
+      <c r="C14" s="17" t="n">
+        <f aca="false">IF(C13="","",C13+IF($B$7="",0,$B$7))</f>
+        <v>33</v>
+      </c>
+      <c r="D14" s="15"/>
+      <c r="E14" s="15"/>
+      <c r="F14" s="17" t="str">
+        <f aca="false">IF(D14="","",D14+IF(E14="",0,E14))</f>
+        <v/>
+      </c>
+      <c r="G14" s="15"/>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="B15" s="19" t="n">
+        <f aca="false">IF(B14="","",B14+IF(WEEKDAY(B14,2)=1,4,3))</f>
+        <v>46290</v>
+      </c>
+      <c r="C15" s="17" t="n">
+        <f aca="false">IF(C14="","",C14+IF($B$7="",0,$B$7))</f>
+        <v>34</v>
+      </c>
+      <c r="D15" s="15"/>
+      <c r="E15" s="15"/>
+      <c r="F15" s="17" t="str">
+        <f aca="false">IF(D15="","",D15+IF(E15="",0,E15))</f>
+        <v/>
+      </c>
+      <c r="G15" s="15"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="B16" s="19" t="n">
+        <f aca="false">IF(B15="","",B15+IF(WEEKDAY(B15,2)=1,4,3))</f>
+        <v>46293</v>
+      </c>
+      <c r="C16" s="17" t="n">
+        <f aca="false">IF(C15="","",C15+IF($B$7="",0,$B$7))</f>
+        <v>35</v>
+      </c>
+      <c r="D16" s="15"/>
+      <c r="E16" s="15"/>
+      <c r="F16" s="17" t="str">
+        <f aca="false">IF(D16="","",D16+IF(E16="",0,E16))</f>
+        <v/>
+      </c>
+      <c r="G16" s="15"/>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="B17" s="19" t="n">
+        <f aca="false">IF(B16="","",B16+IF(WEEKDAY(B16,2)=1,4,3))</f>
+        <v>46297</v>
+      </c>
+      <c r="C17" s="17" t="n">
+        <f aca="false">IF(C16="","",C16+IF($B$7="",0,$B$7))</f>
+        <v>36</v>
+      </c>
+      <c r="D17" s="15"/>
+      <c r="E17" s="15"/>
+      <c r="F17" s="17" t="str">
+        <f aca="false">IF(D17="","",D17+IF(E17="",0,E17))</f>
+        <v/>
+      </c>
+      <c r="G17" s="15"/>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="B18" s="19" t="n">
+        <f aca="false">IF(B17="","",B17+IF(WEEKDAY(B17,2)=1,4,3))</f>
+        <v>46300</v>
+      </c>
+      <c r="C18" s="17" t="n">
+        <f aca="false">IF(C17="","",C17+IF($B$7="",0,$B$7))</f>
+        <v>37</v>
+      </c>
+      <c r="D18" s="15"/>
+      <c r="E18" s="15"/>
+      <c r="F18" s="17" t="str">
+        <f aca="false">IF(D18="","",D18+IF(E18="",0,E18))</f>
+        <v/>
+      </c>
+      <c r="G18" s="15"/>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="B19" s="19" t="n">
+        <f aca="false">IF(B18="","",B18+IF(WEEKDAY(B18,2)=1,4,3))</f>
+        <v>46304</v>
+      </c>
+      <c r="C19" s="17" t="n">
+        <f aca="false">IF(C18="","",C18+IF($B$7="",0,$B$7))</f>
+        <v>38</v>
+      </c>
+      <c r="D19" s="15"/>
+      <c r="E19" s="15"/>
+      <c r="F19" s="17" t="str">
+        <f aca="false">IF(D19="","",D19+IF(E19="",0,E19))</f>
+        <v/>
+      </c>
+      <c r="G19" s="15"/>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="B20" s="19" t="n">
+        <f aca="false">IF(B19="","",B19+IF(WEEKDAY(B19,2)=1,4,3))</f>
+        <v>46307</v>
+      </c>
+      <c r="C20" s="17" t="n">
+        <f aca="false">IF(C19="","",C19+IF($B$7="",0,$B$7))</f>
+        <v>39</v>
+      </c>
+      <c r="D20" s="15"/>
+      <c r="E20" s="15"/>
+      <c r="F20" s="17" t="str">
+        <f aca="false">IF(D20="","",D20+IF(E20="",0,E20))</f>
+        <v/>
+      </c>
+      <c r="G20" s="15"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="B21" s="19" t="n">
+        <f aca="false">IF(B20="","",B20+IF(WEEKDAY(B20,2)=1,4,3))</f>
+        <v>46311</v>
+      </c>
+      <c r="C21" s="17" t="n">
+        <f aca="false">IF(C20="","",C20+IF($B$7="",0,$B$7))</f>
+        <v>40</v>
+      </c>
+      <c r="D21" s="15"/>
+      <c r="E21" s="15"/>
+      <c r="F21" s="17" t="str">
+        <f aca="false">IF(D21="","",D21+IF(E21="",0,E21))</f>
+        <v/>
+      </c>
+      <c r="G21" s="15"/>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="B22" s="19" t="n">
+        <f aca="false">IF(B21="","",B21+IF(WEEKDAY(B21,2)=1,4,3))</f>
+        <v>46314</v>
+      </c>
+      <c r="C22" s="17" t="n">
+        <f aca="false">IF(C21="","",C21+IF($B$7="",0,$B$7))</f>
+        <v>41</v>
+      </c>
+      <c r="D22" s="15"/>
+      <c r="E22" s="15"/>
+      <c r="F22" s="17" t="str">
+        <f aca="false">IF(D22="","",D22+IF(E22="",0,E22))</f>
+        <v/>
+      </c>
+      <c r="G22" s="15"/>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="B23" s="19" t="n">
+        <f aca="false">IF(B22="","",B22+IF(WEEKDAY(B22,2)=1,4,3))</f>
+        <v>46318</v>
+      </c>
+      <c r="C23" s="17" t="n">
+        <f aca="false">IF(C22="","",C22+IF($B$7="",0,$B$7))</f>
+        <v>42</v>
+      </c>
+      <c r="D23" s="15"/>
+      <c r="E23" s="15"/>
+      <c r="F23" s="17" t="str">
+        <f aca="false">IF(D23="","",D23+IF(E23="",0,E23))</f>
+        <v/>
+      </c>
+      <c r="G23" s="15"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="17" t="n">
+        <v>13</v>
+      </c>
+      <c r="B24" s="19" t="n">
+        <f aca="false">IF(B23="","",B23+IF(WEEKDAY(B23,2)=1,4,3))</f>
+        <v>46321</v>
+      </c>
+      <c r="C24" s="17" t="n">
+        <f aca="false">IF(C23="","",C23+IF($B$7="",0,$B$7))</f>
+        <v>43</v>
+      </c>
+      <c r="D24" s="15"/>
+      <c r="E24" s="15"/>
+      <c r="F24" s="17" t="str">
+        <f aca="false">IF(D24="","",D24+IF(E24="",0,E24))</f>
+        <v/>
+      </c>
+      <c r="G24" s="15"/>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="17" t="n">
+        <v>14</v>
+      </c>
+      <c r="B25" s="19" t="n">
+        <f aca="false">IF(B24="","",B24+IF(WEEKDAY(B24,2)=1,4,3))</f>
+        <v>46325</v>
+      </c>
+      <c r="C25" s="17" t="n">
+        <f aca="false">IF(C24="","",C24+IF($B$7="",0,$B$7))</f>
+        <v>44</v>
+      </c>
+      <c r="D25" s="15"/>
+      <c r="E25" s="15"/>
+      <c r="F25" s="17" t="str">
+        <f aca="false">IF(D25="","",D25+IF(E25="",0,E25))</f>
+        <v/>
+      </c>
+      <c r="G25" s="15"/>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="B26" s="19" t="n">
+        <f aca="false">IF(B25="","",B25+IF(WEEKDAY(B25,2)=1,4,3))</f>
+        <v>46328</v>
+      </c>
+      <c r="C26" s="17" t="n">
+        <f aca="false">IF(C25="","",C25+IF($B$7="",0,$B$7))</f>
+        <v>45</v>
+      </c>
+      <c r="D26" s="15"/>
+      <c r="E26" s="15"/>
+      <c r="F26" s="17" t="str">
+        <f aca="false">IF(D26="","",D26+IF(E26="",0,E26))</f>
+        <v/>
+      </c>
+      <c r="G26" s="15"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B27" s="19" t="n">
+        <f aca="false">IF(B26="","",B26+IF(WEEKDAY(B26,2)=1,4,3))</f>
+        <v>46332</v>
+      </c>
+      <c r="C27" s="17" t="n">
+        <f aca="false">IF(C26="","",C26+IF($B$7="",0,$B$7))</f>
+        <v>46</v>
+      </c>
+      <c r="D27" s="15"/>
+      <c r="E27" s="15"/>
+      <c r="F27" s="17" t="str">
+        <f aca="false">IF(D27="","",D27+IF(E27="",0,E27))</f>
+        <v/>
+      </c>
+      <c r="G27" s="15"/>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="17" t="n">
+        <v>17</v>
+      </c>
+      <c r="B28" s="19" t="n">
+        <f aca="false">IF(B27="","",B27+IF(WEEKDAY(B27,2)=1,4,3))</f>
+        <v>46335</v>
+      </c>
+      <c r="C28" s="17" t="n">
+        <f aca="false">IF(C27="","",C27+IF($B$7="",0,$B$7))</f>
+        <v>47</v>
+      </c>
+      <c r="D28" s="15"/>
+      <c r="E28" s="15"/>
+      <c r="F28" s="17" t="str">
+        <f aca="false">IF(D28="","",D28+IF(E28="",0,E28))</f>
+        <v/>
+      </c>
+      <c r="G28" s="15"/>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="17" t="n">
+        <v>18</v>
+      </c>
+      <c r="B29" s="19" t="n">
+        <f aca="false">IF(B28="","",B28+IF(WEEKDAY(B28,2)=1,4,3))</f>
+        <v>46339</v>
+      </c>
+      <c r="C29" s="17" t="n">
+        <f aca="false">IF(C28="","",C28+IF($B$7="",0,$B$7))</f>
+        <v>48</v>
+      </c>
+      <c r="D29" s="15"/>
+      <c r="E29" s="15"/>
+      <c r="F29" s="17" t="str">
+        <f aca="false">IF(D29="","",D29+IF(E29="",0,E29))</f>
+        <v/>
+      </c>
+      <c r="G29" s="15"/>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="17" t="n">
+        <v>19</v>
+      </c>
+      <c r="B30" s="19" t="n">
+        <f aca="false">IF(B29="","",B29+IF(WEEKDAY(B29,2)=1,4,3))</f>
+        <v>46342</v>
+      </c>
+      <c r="C30" s="17" t="n">
+        <f aca="false">IF(C29="","",C29+IF($B$7="",0,$B$7))</f>
+        <v>49</v>
+      </c>
+      <c r="D30" s="15"/>
+      <c r="E30" s="15"/>
+      <c r="F30" s="17" t="str">
+        <f aca="false">IF(D30="","",D30+IF(E30="",0,E30))</f>
+        <v/>
+      </c>
+      <c r="G30" s="15"/>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="B31" s="19" t="n">
+        <f aca="false">IF(B30="","",B30+IF(WEEKDAY(B30,2)=1,4,3))</f>
+        <v>46346</v>
+      </c>
+      <c r="C31" s="17" t="n">
+        <f aca="false">IF(C30="","",C30+IF($B$7="",0,$B$7))</f>
+        <v>50</v>
+      </c>
+      <c r="D31" s="15"/>
+      <c r="E31" s="15"/>
+      <c r="F31" s="17" t="str">
+        <f aca="false">IF(D31="","",D31+IF(E31="",0,E31))</f>
+        <v/>
+      </c>
+      <c r="G31" s="15"/>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="17" t="n">
+        <v>21</v>
+      </c>
+      <c r="B32" s="19" t="n">
+        <f aca="false">IF(B31="","",B31+IF(WEEKDAY(B31,2)=1,4,3))</f>
+        <v>46349</v>
+      </c>
+      <c r="C32" s="17" t="n">
+        <f aca="false">IF(C31="","",C31+IF($B$7="",0,$B$7))</f>
+        <v>51</v>
+      </c>
+      <c r="D32" s="15"/>
+      <c r="E32" s="15"/>
+      <c r="F32" s="17" t="str">
+        <f aca="false">IF(D32="","",D32+IF(E32="",0,E32))</f>
+        <v/>
+      </c>
+      <c r="G32" s="15"/>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="17" t="n">
+        <v>22</v>
+      </c>
+      <c r="B33" s="19" t="n">
+        <f aca="false">IF(B32="","",B32+IF(WEEKDAY(B32,2)=1,4,3))</f>
+        <v>46353</v>
+      </c>
+      <c r="C33" s="17" t="n">
+        <f aca="false">IF(C32="","",C32+IF($B$7="",0,$B$7))</f>
+        <v>52</v>
+      </c>
+      <c r="D33" s="15"/>
+      <c r="E33" s="15"/>
+      <c r="F33" s="17" t="str">
+        <f aca="false">IF(D33="","",D33+IF(E33="",0,E33))</f>
+        <v/>
+      </c>
+      <c r="G33" s="15"/>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="17" t="n">
+        <v>23</v>
+      </c>
+      <c r="B34" s="19" t="n">
+        <f aca="false">IF(B33="","",B33+IF(WEEKDAY(B33,2)=1,4,3))</f>
+        <v>46356</v>
+      </c>
+      <c r="C34" s="17" t="n">
+        <f aca="false">IF(C33="","",C33+IF($B$7="",0,$B$7))</f>
+        <v>53</v>
+      </c>
+      <c r="D34" s="15"/>
+      <c r="E34" s="15"/>
+      <c r="F34" s="17" t="str">
+        <f aca="false">IF(D34="","",D34+IF(E34="",0,E34))</f>
+        <v/>
+      </c>
+      <c r="G34" s="15"/>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="17" t="n">
+        <v>24</v>
+      </c>
+      <c r="B35" s="19" t="n">
+        <f aca="false">IF(B34="","",B34+IF(WEEKDAY(B34,2)=1,4,3))</f>
+        <v>46360</v>
+      </c>
+      <c r="C35" s="17" t="n">
+        <f aca="false">IF(C34="","",C34+IF($B$7="",0,$B$7))</f>
+        <v>54</v>
+      </c>
+      <c r="D35" s="15"/>
+      <c r="E35" s="15"/>
+      <c r="F35" s="17" t="str">
+        <f aca="false">IF(D35="","",D35+IF(E35="",0,E35))</f>
+        <v/>
+      </c>
+      <c r="G35" s="15"/>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="D36" s="17" t="n">
+        <f aca="false">MAX(D12:D35)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="F37" s="17" t="n">
+        <f aca="false">MAX(F12:F35)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="F38" s="17" t="n">
+        <f aca="false">SUM(F12:F35)</f>
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="B9:G9"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
 </file>